--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -473,720 +473,720 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4CeeEOM32jQcH3eN9Q2dGj</t>
+          <t>4u7EnebtmKWzUH433cf5Qv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nevermind (Remastered)</t>
+          <t>A Night At The Opera (2011 Remaster)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Smells Like Teen Spirit</t>
+          <t>Bohemian Rhapsody - Remastered 2011</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>301920</v>
+        <v>354320</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2RsAajgo0g7bMCHxwH3Sk0</t>
+          <t>5T8EDUDqKcs6OSOwEsfqG7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nevermind (Remastered)</t>
+          <t>Jazz (2011 Remaster)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Come As You Are</t>
+          <t>Don't Stop Me Now - Remastered 2011</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>218920</v>
+        <v>209413</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11LmqTE2naFULdEP94AUBa</t>
+          <t>2fuCquhmrzHpu5xcA1ci9x</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>In Utero (Deluxe Edition)</t>
+          <t>Hot Space (2011 Remaster)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Heart-Shaped Box</t>
+          <t>Under Pressure - Remastered 2011</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>281160</v>
+        <v>248440</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5vHLwhxxlGzmClMcxRRFPr</t>
+          <t>5vdp5UmvTsnMEMESIF2Ym7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nevermind (Remastered)</t>
+          <t>The Game (2011 Remaster)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Another One Bites The Dust - Remastered 2011</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>257053</v>
+        <v>214653</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2SHTKB8YYlawTGIuJ2b2ok</t>
+          <t>4pbJqGIASGPr0ZpGpnWkDn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>News Of The World (2011 Remaster)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>About A Girl</t>
+          <t>We Will Rock You - Remastered 2011</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>168428</v>
+        <v>122066</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15VRO9CQwMpbqUYA7e6Hwg</t>
+          <t>6xdLJrVj4vIXwhuG8TMopk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MTV Unplugged In New York</t>
+          <t>The Game (2011 Remaster)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Man Who Sold The World - Live</t>
+          <t>Crazy Little Thing Called Love - Remastered 2011</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>261093</v>
+        <v>163373</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4gHnSNHs8RyVukKoWdS99f</t>
+          <t>4rDbp1vnvEhieiccprPMdI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nevermind (Remastered)</t>
+          <t>A Day At The Races (Deluxe Edition 2011 Remaster)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Something In The Way</t>
+          <t>Somebody To Love - Remastered 2011</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>232146</v>
+        <v>296480</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2mvffzYUJ9Ld9xhsF5DUjU</t>
+          <t>4cIPLtg1avt2Jm3ne9S1zy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nevermind (Remastered)</t>
+          <t>Sheer Heart Attack (Deluxe Edition 2011 Remaster)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>In Bloom</t>
+          <t>Killer Queen - Remastered 2011</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>255080</v>
+        <v>179600</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1Ic9pKxGSJGM0LKeqf6lGe</t>
+          <t>1lCRw5FEZ1gPDNPzy1K4zW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In Utero</t>
+          <t>News Of The World (2011 Remaster)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>All Apologies</t>
+          <t>We Are The Champions - Remastered 2011</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>233173</v>
+        <v>179200</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5gRcv46AMTrosmTOqrOV3Q</t>
+          <t>1nQRg9q9uwALGzouOX5OyQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nirvana</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>In Utero</t>
+          <t>The Works (2011 Remaster)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dumb</t>
+          <t>Radio Ga Ga - Remastered 2011</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F11" t="n">
-        <v>151893</v>
+        <v>348226</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>grunge, rock</t>
+          <t>classic rock, rock, glam rock</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7snQQk1zcKl8gZ92AnueZW</t>
+          <t>0TwBtDAWpkpM3srywFVOV5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Appetite For Destruction</t>
+          <t>Dangerously In Love</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sweet Child O' Mine</t>
+          <t>Crazy In Love (feat. JAY-Z)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>356066</v>
+        <v>235933</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0G21yYKMZoHa30cYVi1iA8</t>
+          <t>2MfOcbtgz2yTsiznFmVZUN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Appetite For Destruction</t>
+          <t>I AM...SASHA FIERCE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Welcome To The Jungle</t>
+          <t>Halo</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>273480</v>
+        <v>261640</v>
       </c>
       <c r="G13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6eN1f9KNmiWEhpE2RhQqB5</t>
+          <t>7wLShogStyDeZvL0a6daN5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Appetite For Destruction</t>
+          <t>COWBOY CARTER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paradise City</t>
+          <t>TEXAS HOLD 'EM</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F14" t="n">
-        <v>405600</v>
+        <v>233456</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3YRCqOhFifThpSRFJ1VWFM</t>
+          <t>2zOu7jpi6s33p7aEuFDCHh</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Use Your Illusion I</t>
+          <t>I AM...SASHA FIERCE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>November Rain</t>
+          <t>Diva</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>536066</v>
+        <v>200613</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4JiEyzf0Md7KEFFGWDDdCr</t>
+          <t>5mMjkxGijQB4JZallYrkOW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Use Your Illusion II</t>
+          <t>I AM...SASHA FIERCE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Knockin' On Heaven's Door</t>
+          <t>Single Ladies (Put a Ring on It)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>336000</v>
+        <v>193213</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2N2yrmodOnVF10mKvItC9P</t>
+          <t>0K7wIocSvzcRISpssBUzfZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use Your Illusion I</t>
+          <t>I AM...SASHA FIERCE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Don't Cry (Original)</t>
+          <t>If I Were a Boy</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>283733</v>
+        <v>249146</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1OEoNpiyqBghuEUaT6Je6U</t>
+          <t>1G7DcLzPnopdZjLkev0K4e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Appetite For Destruction (Super Deluxe Edition)</t>
+          <t>B'Day</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Patience</t>
+          <t>Irreplaceable</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>354880</v>
+        <v>227666</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0rFWuqFgHAfuzE8uSB9TWR</t>
+          <t>1xzi1Jcr7mEi9K2RfzLOqS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Use Your Illusion I</t>
+          <t>RENAISSANCE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Live And Let Die</t>
+          <t>CUFF IT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>182733</v>
+        <v>225388</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0dlTGl67UFWcKupzkxZYOn</t>
+          <t>7oAuqs6akGnPU3Tb00ZmyM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Use Your Illusion II</t>
+          <t>Lemonade</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>You Could Be Mine</t>
+          <t>All Night</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
-        <v>343640</v>
+        <v>322000</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6i4Qi1mJxXjqNIL9HfJhRs</t>
+          <t>1z6WtY7X4HQJvzxC4UgkSf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guns N' Roses</t>
+          <t>Beyoncé</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Use Your Illusion II</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Civil War</t>
+          <t>Love On Top</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F21" t="n">
-        <v>462093</v>
+        <v>267413</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>rock, glam metal, hard rock, classic rock</t>
+          <t>Desconocido</t>
         </is>
       </c>
     </row>
